--- a/gte/nodes/HPT/turbine_stage_1_blade_rotor_coordinates_foil.xlsx
+++ b/gte/nodes/HPT/turbine_stage_1_blade_rotor_coordinates_foil.xlsx
@@ -349,647 +349,647 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>1.0651915093945702E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.0009594392169575205</v>
+        <v>0.00095925308721746521</v>
       </c>
       <c r="B2">
-        <v>0.0033157313578730677</v>
+        <v>0.0033112285934832307</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.001918878433915041</v>
+        <v>0.0019185061744349304</v>
       </c>
       <c r="B3">
-        <v>0.0053493369919403446</v>
+        <v>0.0053422273230553426</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>0.002878317650872562</v>
+        <v>0.0028777592616523961</v>
       </c>
       <c r="B4">
-        <v>0.0069849597440456686</v>
+        <v>0.0069760579528388355</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>0.003837756867830082</v>
+        <v>0.0038370123488698608</v>
       </c>
       <c r="B5">
-        <v>0.0083499670364863519</v>
+        <v>0.0083397477326907412</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>0.0047971960847876024</v>
+        <v>0.004796265436087326</v>
       </c>
       <c r="B6">
-        <v>0.0095182703983786553</v>
+        <v>0.0095070253329170209</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>0.0057566353017451241</v>
+        <v>0.0057555185233047921</v>
       </c>
       <c r="B7">
-        <v>0.010521896918738899</v>
+        <v>0.010509837376129021</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>0.006716074518702644</v>
+        <v>0.0067147716105222573</v>
       </c>
       <c r="B8">
-        <v>0.01139794295513435</v>
+        <v>0.011385211943628465</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>0.007675513735660164</v>
+        <v>0.0076740246977397217</v>
       </c>
       <c r="B9">
-        <v>0.012160691725720256</v>
+        <v>0.012147402813775431</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>0.0086349529526176839</v>
+        <v>0.0086332777849571878</v>
       </c>
       <c r="B10">
-        <v>0.012822037191659095</v>
+        <v>0.01280828203585291</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>0.0095943921695752048</v>
+        <v>0.0095925308721746521</v>
       </c>
       <c r="B11">
-        <v>0.013391943966576286</v>
+        <v>0.013377797812385732</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>0.010553831386532726</v>
+        <v>0.010551783959392118</v>
       </c>
       <c r="B12">
-        <v>0.013878806099575865</v>
+        <v>0.013864331811113592</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>0.011513270603490248</v>
+        <v>0.011511037046609584</v>
       </c>
       <c r="B13">
-        <v>0.014289729271645516</v>
+        <v>0.014274980298692973</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>0.012472709820447767</v>
+        <v>0.012470290133827049</v>
       </c>
       <c r="B14">
-        <v>0.014630755313453881</v>
+        <v>0.014615777890138808</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>0.013432149037405288</v>
+        <v>0.013429543221044515</v>
       </c>
       <c r="B15">
-        <v>0.014907043907244337</v>
+        <v>0.014891878691987836</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>0.014391588254362807</v>
+        <v>0.014388796308261977</v>
       </c>
       <c r="B16">
-        <v>0.01512302337743901</v>
+        <v>0.015107706681788541</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>0.015351027471320328</v>
+        <v>0.015348049395479443</v>
       </c>
       <c r="B17">
-        <v>0.015282520383016784</v>
+        <v>0.015267085091445568</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>0.016310466688277851</v>
+        <v>0.016307302482696909</v>
       </c>
       <c r="B18">
-        <v>0.015388877023057437</v>
+        <v>0.015373353271426339</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>0.017269905905235368</v>
+        <v>0.017266555569914376</v>
       </c>
       <c r="B19">
-        <v>0.015427570482010438</v>
+        <v>0.015411995662077023</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>0.018229345122192889</v>
+        <v>0.018225808657131842</v>
       </c>
       <c r="B20">
-        <v>0.015415769875027987</v>
+        <v>0.015400171488293653</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>0.01918878433915041</v>
+        <v>0.019185061744349304</v>
       </c>
       <c r="B21">
-        <v>0.015356509379212131</v>
+        <v>0.015340913246227085</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>0.02014822355610793</v>
+        <v>0.02014431483156677</v>
       </c>
       <c r="B22">
-        <v>0.015251759689424124</v>
+        <v>0.015236190591945455</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>0.021107662773065451</v>
+        <v>0.021103567918784236</v>
       </c>
       <c r="B23">
-        <v>0.015085859387220549</v>
+        <v>0.015070350976316817</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>0.022067101990022972</v>
+        <v>0.022062821006001702</v>
       </c>
       <c r="B24">
-        <v>0.014867577159959684</v>
+        <v>0.014852159046375052</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>0.023026541206980496</v>
+        <v>0.023022074093219169</v>
       </c>
       <c r="B25">
-        <v>0.014605550733598481</v>
+        <v>0.014590248290152942</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>0.023985980423938014</v>
+        <v>0.023981327180436631</v>
       </c>
       <c r="B26">
-        <v>0.014297548260717444</v>
+        <v>0.014282388609860261</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>0.024945419640895534</v>
+        <v>0.024940580267654097</v>
       </c>
       <c r="B27">
-        <v>0.013917724643043507</v>
+        <v>0.01390275274901304</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>0.025904858857853055</v>
+        <v>0.025899833354871563</v>
       </c>
       <c r="B28">
-        <v>0.013492697023263771</v>
+        <v>0.013477943281118105</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>0.026864298074810576</v>
+        <v>0.026859086442089029</v>
       </c>
       <c r="B29">
-        <v>0.013023398525358812</v>
+        <v>0.013008893285225906</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>0.027823737291768097</v>
+        <v>0.027818339529306495</v>
       </c>
       <c r="B30">
-        <v>0.012473723487314207</v>
+        <v>0.012459526616456228</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>0.028783176508725614</v>
+        <v>0.028777592616523955</v>
       </c>
       <c r="B31">
-        <v>0.011867048082079052</v>
+        <v>0.011853207321238684</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>0.029742615725683135</v>
+        <v>0.029736845703741421</v>
       </c>
       <c r="B32">
-        <v>0.011209986671048972</v>
+        <v>0.011196545775267039</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>0.030702054942640656</v>
+        <v>0.030696098790958887</v>
       </c>
       <c r="B33">
-        <v>0.010457707963590369</v>
+        <v>0.010444758744363649</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>0.03166149415959818</v>
+        <v>0.031655351878176356</v>
       </c>
       <c r="B34">
-        <v>0.0096282398010256731</v>
+        <v>0.0096158703521051977</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>0.0326209333765557</v>
+        <v>0.032614604965393819</v>
       </c>
       <c r="B35">
-        <v>0.0087344157199208891</v>
+        <v>0.0087227036472689815</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>0.033580372593513215</v>
+        <v>0.033573858052611281</v>
       </c>
       <c r="B36">
-        <v>0.0077042117967140765</v>
+        <v>0.00769334783100365</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>0.034539811810470736</v>
+        <v>0.034533111139828751</v>
       </c>
       <c r="B37">
-        <v>0.006558276551979941</v>
+        <v>0.0065484686357738676</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>0.035499251027428257</v>
+        <v>0.035492364227046214</v>
       </c>
       <c r="B38">
-        <v>0.0053137002204367446</v>
+        <v>0.0053051374793420276</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>0.036458690244385777</v>
+        <v>0.036451617314263683</v>
       </c>
       <c r="B39">
-        <v>0.0038068292801643031</v>
+        <v>0.0038001629779432678</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>0.037418129461343305</v>
+        <v>0.037410870401481146</v>
       </c>
       <c r="B40">
-        <v>0.0022999583398918616</v>
+        <v>0.0022951884765445079</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>0.038377568678300819</v>
+        <v>0.038370123488698608</v>
       </c>
       <c r="B41">
-        <v>0.00079308739961942679</v>
+        <v>0.00079021397514575484</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>0.038377568678300819</v>
+        <v>0.038370123488698608</v>
       </c>
       <c r="B42">
-        <v>0.000630420746580596</v>
+        <v>0.000627578879188718</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>0.037418129461343305</v>
+        <v>0.037410870401481146</v>
       </c>
       <c r="B43">
-        <v>0.001781429280380999</v>
+        <v>0.0017767600108777911</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>0.036458690244385777</v>
+        <v>0.036451617314263683</v>
       </c>
       <c r="B44">
-        <v>0.0029324378141814067</v>
+        <v>0.0029259411425668694</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>0.035499251027428257</v>
+        <v>0.035492364227046214</v>
       </c>
       <c r="B45">
-        <v>0.0040834463479818154</v>
+        <v>0.0040751222742559474</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>0.034539811810470736</v>
+        <v>0.034533111139828751</v>
       </c>
       <c r="B46">
-        <v>0.0049868051969354996</v>
+        <v>0.0049773021437678026</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>0.033580372593513215</v>
+        <v>0.033573858052611281</v>
       </c>
       <c r="B47">
-        <v>0.0057985638441576323</v>
+        <v>0.005788069571234177</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>0.0326209333765557</v>
+        <v>0.032614604965393819</v>
       </c>
       <c r="B48">
-        <v>0.0065032353218651114</v>
+        <v>0.006491956094796505</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>0.03166149415959818</v>
+        <v>0.031655351878176356</v>
       </c>
       <c r="B49">
-        <v>0.0070841034954935911</v>
+        <v>0.0070722276051236157</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>0.030702054942640656</v>
+        <v>0.030696098790958887</v>
       </c>
       <c r="B50">
-        <v>0.0076073580765549324</v>
+        <v>0.0075949618208449865</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>0.029742615725683135</v>
+        <v>0.029736845703741421</v>
       </c>
       <c r="B51">
-        <v>0.0080618349878869427</v>
+        <v>0.0080490048287145659</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>0.028783176508725614</v>
+        <v>0.028777592616523955</v>
       </c>
       <c r="B52">
-        <v>0.0084330580807831287</v>
+        <v>0.0084198835087486781</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>0.027823737291768097</v>
+        <v>0.027818339529306495</v>
       </c>
       <c r="B53">
-        <v>0.0087608820657420136</v>
+        <v>0.0087474054804388135</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>0.026864298074810576</v>
+        <v>0.026859086442089029</v>
       </c>
       <c r="B54">
-        <v>0.00903984870727957</v>
+        <v>0.0090261162697161564</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>0.025904858857853055</v>
+        <v>0.025899833354871563</v>
       </c>
       <c r="B55">
-        <v>0.0092513898487726239</v>
+        <v>0.0092374589137292022</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>0.024945419640895534</v>
+        <v>0.024940580267654097</v>
       </c>
       <c r="B56">
-        <v>0.0094265467883228714</v>
+        <v>0.0094124461759242852</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>0.023985980423938014</v>
+        <v>0.023981327180436631</v>
       </c>
       <c r="B57">
-        <v>0.0095647473526259113</v>
+        <v>0.0095505058579032544</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>0.023026541206980496</v>
+        <v>0.023022074093219169</v>
       </c>
       <c r="B58">
-        <v>0.00964563097492603</v>
+        <v>0.0096312907483245176</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>0.022067101990022972</v>
+        <v>0.022062821006001702</v>
       </c>
       <c r="B59">
-        <v>0.0096908631085367378</v>
+        <v>0.00967644926955721</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>0.021107662773065451</v>
+        <v>0.021103567918784236</v>
       </c>
       <c r="B60">
-        <v>0.0097025932970898413</v>
+        <v>0.00968812923157068</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>0.02014822355610793</v>
+        <v>0.02014431483156677</v>
       </c>
       <c r="B61">
-        <v>0.00967495326520647</v>
+        <v>0.0096604660596410468</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>0.01918878433915041</v>
+        <v>0.019185061744349304</v>
       </c>
       <c r="B62">
-        <v>0.0096028633474546151</v>
+        <v>0.0095883834129960963</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>0.018229345122192889</v>
+        <v>0.018225808657131842</v>
       </c>
       <c r="B63">
-        <v>0.0094986640104462554</v>
+        <v>0.00948421353319591</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>0.017269905905235368</v>
+        <v>0.017266555569914376</v>
       </c>
       <c r="B64">
-        <v>0.0093615997548050986</v>
+        <v>0.00934720172391124</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>0.016310466688277851</v>
+        <v>0.016307302482696909</v>
       </c>
       <c r="B65">
-        <v>0.0091903708454330654</v>
+        <v>0.0091760495945161155</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>0.015351027471320328</v>
+        <v>0.015348049395479443</v>
       </c>
       <c r="B66">
-        <v>0.0089750301339447582</v>
+        <v>0.0089608184858307946</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>0.014391588254362807</v>
+        <v>0.014388796308261977</v>
       </c>
       <c r="B67">
-        <v>0.0087262905077323313</v>
+        <v>0.0087122147684709685</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>0.013432149037405288</v>
+        <v>0.013429543221044515</v>
       </c>
       <c r="B68">
-        <v>0.0084429601591358878</v>
+        <v>0.008429048966235848</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>0.012472709820447767</v>
+        <v>0.012470290133827049</v>
       </c>
       <c r="B69">
-        <v>0.0081237162233141254</v>
+        <v>0.0081100011556261425</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>0.011513270603490248</v>
+        <v>0.011511037046609584</v>
       </c>
       <c r="B70">
-        <v>0.00776704359620813</v>
+        <v>0.0077535600142962808</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>0.010553831386532726</v>
+        <v>0.010551783959392118</v>
       </c>
       <c r="B71">
-        <v>0.007371171515390019</v>
+        <v>0.0073579596980797692</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>0.0095943921695752048</v>
+        <v>0.0095925308721746521</v>
       </c>
       <c r="B72">
-        <v>0.0069340067421363024</v>
+        <v>0.006921113417886024</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>0.0086349529526176839</v>
+        <v>0.0086332777849571878</v>
       </c>
       <c r="B73">
-        <v>0.0064530645784498771</v>
+        <v>0.0064405449935855154</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>0.007675513735660164</v>
+        <v>0.0076740246977397217</v>
       </c>
       <c r="B74">
-        <v>0.0059254023707125845</v>
+        <v>0.0059133230953620358</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>0.006716074518702644</v>
+        <v>0.0067147716105222573</v>
       </c>
       <c r="B75">
-        <v>0.005347565677988571</v>
+        <v>0.0053360084304167931</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>0.0057566353017451241</v>
+        <v>0.0057555185233047921</v>
       </c>
       <c r="B76">
-        <v>0.0047155667503896307</v>
+        <v>0.0047046336269481676</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>0.0047971960847876024</v>
+        <v>0.004796265436087326</v>
       </c>
       <c r="B77">
-        <v>0.0040249316080832286</v>
+        <v>0.0040147522419415752</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>0.003837756867830082</v>
+        <v>0.0038370123488698608</v>
       </c>
       <c r="B78">
-        <v>0.0032627932410055748</v>
+        <v>0.0032535608411424204</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>0.002878317650872562</v>
+        <v>0.0028777592616523961</v>
       </c>
       <c r="B79">
-        <v>0.00242218761233194</v>
+        <v>0.002414170991937178</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>0.001918878433915041</v>
+        <v>0.0019185061744349304</v>
       </c>
       <c r="B80">
-        <v>0.00149090962630698</v>
+        <v>0.0014845484864271449</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>0.0009594392169575205</v>
+        <v>0.00095925308721746521</v>
       </c>
       <c r="B81">
-        <v>0.00047883313121555271</v>
+        <v>0.00047488072074095949</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>1.0651915093945702E-18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1015,647 +1015,647 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-9.4937278888095369E-19</v>
+        <v>9.4918861201254331E-19</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.00085511898764799039</v>
+        <v>0.00085495309587280176</v>
       </c>
       <c r="B2">
-        <v>0.0025163391954579556</v>
+        <v>0.002515882130350677</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.0017102379752959808</v>
+        <v>0.0017099061917456035</v>
       </c>
       <c r="B3">
-        <v>0.0041377168848313241</v>
+        <v>0.0041369644168220291</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>0.0025653569629439715</v>
+        <v>0.0025648592876184053</v>
       </c>
       <c r="B4">
-        <v>0.0054645650767604255</v>
+        <v>0.0054635684611071232</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>0.0034204759505919616</v>
+        <v>0.003419812383491207</v>
       </c>
       <c r="B5">
-        <v>0.0065849159187276853</v>
+        <v>0.0065837116601755417</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>0.0042755949382399516</v>
+        <v>0.0042747654793640084</v>
       </c>
       <c r="B6">
-        <v>0.0075520302072971824</v>
+        <v>0.007550645817259098</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>0.005130713925887943</v>
+        <v>0.0051297185752368106</v>
       </c>
       <c r="B7">
-        <v>0.0083890736549485125</v>
+        <v>0.0083875327604246049</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>0.0059858329135359326</v>
+        <v>0.0059846716711096119</v>
       </c>
       <c r="B8">
-        <v>0.009124252513537259</v>
+        <v>0.0091225737956845462</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>0.0068409519011839231</v>
+        <v>0.0068396247669824141</v>
       </c>
       <c r="B9">
-        <v>0.0097682528897673759</v>
+        <v>0.0097664531883094822</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>0.0076960708888319128</v>
+        <v>0.0076945778628552154</v>
       </c>
       <c r="B10">
-        <v>0.010330092974202156</v>
+        <v>0.010328187552923409</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>0.0085511898764799033</v>
+        <v>0.0085495309587280167</v>
       </c>
       <c r="B11">
-        <v>0.010817410439612582</v>
+        <v>0.010815413210855997</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>0.0094063088641278946</v>
+        <v>0.00940448405460082</v>
       </c>
       <c r="B12">
-        <v>0.011236695740818852</v>
+        <v>0.011234619455836536</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>0.010261427851775886</v>
+        <v>0.010259437150473621</v>
       </c>
       <c r="B13">
-        <v>0.011593482346223188</v>
+        <v>0.011591338756880884</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>0.011116546839423874</v>
+        <v>0.011114390246346423</v>
       </c>
       <c r="B14">
-        <v>0.011892503074083138</v>
+        <v>0.01189030307033882</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>0.011971665827071865</v>
+        <v>0.011969343342219224</v>
       </c>
       <c r="B15">
-        <v>0.012137820353637394</v>
+        <v>0.012135574080260626</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>0.012826784814719855</v>
+        <v>0.012824296438092025</v>
       </c>
       <c r="B16">
-        <v>0.012332937182835306</v>
+        <v>0.01233065413795879</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>0.013681903802367846</v>
+        <v>0.013679249533964828</v>
       </c>
       <c r="B17">
-        <v>0.012480894797194865</v>
+        <v>0.012478583914459959</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>0.014537022790015838</v>
+        <v>0.01453420262983763</v>
       </c>
       <c r="B18">
-        <v>0.012584362659832062</v>
+        <v>0.012582032375066414</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>0.015392141777663826</v>
+        <v>0.015389155725710431</v>
       </c>
       <c r="B19">
-        <v>0.012630977667548839</v>
+        <v>0.012628638770604118</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>0.016247260765311817</v>
+        <v>0.016244108821583232</v>
       </c>
       <c r="B20">
-        <v>0.012635019661406913</v>
+        <v>0.012632680236252872</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>0.017102379752959807</v>
+        <v>0.017099061917456033</v>
       </c>
       <c r="B21">
-        <v>0.012598966918581389</v>
+        <v>0.012596634579109506</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>0.017957498740607796</v>
+        <v>0.017954015013328835</v>
       </c>
       <c r="B22">
-        <v>0.012524421891706571</v>
+        <v>0.012522103947381551</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>0.018812617728255789</v>
+        <v>0.01880896810920164</v>
       </c>
       <c r="B23">
-        <v>0.012398010934486822</v>
+        <v>0.012395717231550862</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>0.019667736715903779</v>
+        <v>0.019663921205074441</v>
       </c>
       <c r="B24">
-        <v>0.012227066941552229</v>
+        <v>0.012224805927119062</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>0.020522855703551772</v>
+        <v>0.020518874300947242</v>
       </c>
       <c r="B25">
-        <v>0.012018893526769341</v>
+        <v>0.012016672256675871</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>0.021377974691199758</v>
+        <v>0.02137382739682004</v>
       </c>
       <c r="B26">
-        <v>0.011771563114207281</v>
+        <v>0.011769389005442122</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>0.022233093678847748</v>
+        <v>0.022228780492692845</v>
       </c>
       <c r="B27">
-        <v>0.011462996091748594</v>
+        <v>0.011460880719565372</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>0.023088212666495741</v>
+        <v>0.023083733588565646</v>
       </c>
       <c r="B28">
-        <v>0.011115876939106414</v>
+        <v>0.011113827571431891</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>0.02394333165414373</v>
+        <v>0.023938686684438448</v>
       </c>
       <c r="B29">
-        <v>0.010731004307941137</v>
+        <v>0.010729028056755597</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>0.024798450641791724</v>
+        <v>0.024793639780311252</v>
       </c>
       <c r="B30">
-        <v>0.010277630968623948</v>
+        <v>0.010275740694044971</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>0.02565356962943971</v>
+        <v>0.02564859287618405</v>
       </c>
       <c r="B31">
-        <v>0.0097757755365891139</v>
+        <v>0.009773980291988978</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>0.0265086886170877</v>
+        <v>0.026503545972056852</v>
       </c>
       <c r="B32">
-        <v>0.009231101690429306</v>
+        <v>0.00922940945744657</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>0.027363807604735692</v>
+        <v>0.027358499067929656</v>
       </c>
       <c r="B33">
-        <v>0.0086057332974601441</v>
+        <v>0.0086041590351283274</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>0.028218926592383682</v>
+        <v>0.028213452163802458</v>
       </c>
       <c r="B34">
-        <v>0.00791533452640335</v>
+        <v>0.00791389016776828</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>0.029074045580031675</v>
+        <v>0.029068405259675259</v>
       </c>
       <c r="B35">
-        <v>0.0071708448820940671</v>
+        <v>0.0071695403164999</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>0.029929164567679661</v>
+        <v>0.02992335835554806</v>
       </c>
       <c r="B36">
-        <v>0.0063125342772415828</v>
+        <v>0.0063113900844773566</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>0.030784283555327651</v>
+        <v>0.030778311451420862</v>
       </c>
       <c r="B37">
-        <v>0.00535910942781973</v>
+        <v>0.0053581424176796606</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>0.031639402542975641</v>
+        <v>0.031633264547293663</v>
       </c>
       <c r="B38">
-        <v>0.0043249994587778763</v>
+        <v>0.004324223797133625</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>0.032494521530623634</v>
+        <v>0.032488217643166464</v>
       </c>
       <c r="B39">
-        <v>0.0030811258061892808</v>
+        <v>0.0030805771449280259</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>0.033349640518271627</v>
+        <v>0.033343170739039266</v>
       </c>
       <c r="B40">
-        <v>0.0018372521536006851</v>
+        <v>0.0018369304927224267</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>0.034204759505919613</v>
+        <v>0.034198123834912067</v>
       </c>
       <c r="B41">
-        <v>0.00059337850101209464</v>
+        <v>0.00059328384051683246</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>0.034204759505919613</v>
+        <v>0.034198123834912067</v>
       </c>
       <c r="B42">
-        <v>0.00048251156493490227</v>
+        <v>0.00048243841245560284</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>0.033349640518271627</v>
+        <v>0.033343170739039266</v>
       </c>
       <c r="B43">
-        <v>0.0014838439594747853</v>
+        <v>0.001483590859245439</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>0.032494521530623634</v>
+        <v>0.032488217643166464</v>
       </c>
       <c r="B44">
-        <v>0.0024851763540146726</v>
+        <v>0.0024847433060352793</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>0.031639402542975641</v>
+        <v>0.031633264547293663</v>
       </c>
       <c r="B45">
-        <v>0.00348650874855456</v>
+        <v>0.0034858957528251197</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>0.030784283555327651</v>
+        <v>0.030778311451420862</v>
       </c>
       <c r="B46">
-        <v>0.0042880588405474823</v>
+        <v>0.0042872996125825312</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>0.029929164567679661</v>
+        <v>0.02992335835554806</v>
       </c>
       <c r="B47">
-        <v>0.005013722592149163</v>
+        <v>0.0050128303668645381</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>0.029074045580031675</v>
+        <v>0.029068405259675259</v>
       </c>
       <c r="B48">
-        <v>0.0056501635995641741</v>
+        <v>0.0056491540438120269</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>0.028218926592383682</v>
+        <v>0.028213452163802458</v>
       </c>
       <c r="B49">
-        <v>0.0061813553002508462</v>
+        <v>0.0061802473309324948</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>0.027363807604735692</v>
+        <v>0.027358499067929656</v>
       </c>
       <c r="B50">
-        <v>0.0066630514212420704</v>
+        <v>0.0066618540362217505</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>0.0265086886170877</v>
+        <v>0.026503545972056852</v>
       </c>
       <c r="B51">
-        <v>0.0070854502929353609</v>
+        <v>0.0070841743130406849</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>0.02565356962943971</v>
+        <v>0.02564859287618405</v>
       </c>
       <c r="B52">
-        <v>0.0074353084349975517</v>
+        <v>0.0074339672374339819</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>0.024798450641791724</v>
+        <v>0.024793639780311252</v>
       </c>
       <c r="B53">
-        <v>0.0077471101466830561</v>
+        <v>0.0077457107892715937</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>0.02394333165414373</v>
+        <v>0.023938686684438448</v>
       </c>
       <c r="B54">
-        <v>0.0080159797175238523</v>
+        <v>0.0080145301769546009</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>0.023088212666495741</v>
+        <v>0.023083733588565646</v>
       </c>
       <c r="B55">
-        <v>0.0082251754793192088</v>
+        <v>0.0082236869033048311</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>0.022233093678847748</v>
+        <v>0.022228780492692845</v>
       </c>
       <c r="B56">
-        <v>0.00840199299843633</v>
+        <v>0.0084004714561695774</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>0.021377974691199758</v>
+        <v>0.02137382739682004</v>
       </c>
       <c r="B57">
-        <v>0.00854587963242933</v>
+        <v>0.008544331301324027</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>0.020522855703551772</v>
+        <v>0.020518874300947242</v>
       </c>
       <c r="B58">
-        <v>0.0086384151277856518</v>
+        <v>0.0086368496653291254</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>0.019667736715903779</v>
+        <v>0.019663921205074441</v>
       </c>
       <c r="B59">
-        <v>0.0086988304216060845</v>
+        <v>0.0086972538796592416</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>0.018812617728255789</v>
+        <v>0.01880896810920164</v>
       </c>
       <c r="B60">
-        <v>0.0087289969949268346</v>
+        <v>0.0087274150750812039</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>0.017957498740607796</v>
+        <v>0.017954015013328835</v>
       </c>
       <c r="B61">
-        <v>0.0087234987780981463</v>
+        <v>0.0087219182070413862</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>0.017102379752959807</v>
+        <v>0.017099061917456033</v>
       </c>
       <c r="B62">
-        <v>0.0086775171629183238</v>
+        <v>0.008675945578698838</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>0.016247260765311817</v>
+        <v>0.016244108821583232</v>
       </c>
       <c r="B63">
-        <v>0.0086021623707736358</v>
+        <v>0.0086006053137633147</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>0.015392141777663826</v>
+        <v>0.015389155725710431</v>
       </c>
       <c r="B64">
-        <v>0.00849666017655912</v>
+        <v>0.0084951233308817441</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>0.014537022790015838</v>
+        <v>0.01453420262983763</v>
       </c>
       <c r="B65">
-        <v>0.0083597144278141824</v>
+        <v>0.0083582037183414226</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>0.013681903802367846</v>
+        <v>0.013679249533964828</v>
       </c>
       <c r="B66">
-        <v>0.0081819674805772985</v>
+        <v>0.0081804905831640365</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>0.012826784814719855</v>
+        <v>0.012824296438092025</v>
       </c>
       <c r="B67">
-        <v>0.0079731857468765648</v>
+        <v>0.00797174848710778</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>0.011971665827071865</v>
+        <v>0.011969343342219224</v>
       </c>
       <c r="B68">
-        <v>0.0077321653142601345</v>
+        <v>0.0077307737312199264</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>0.011116546839423874</v>
+        <v>0.011114390246346423</v>
       </c>
       <c r="B69">
-        <v>0.0074575714308648833</v>
+        <v>0.0074562317970734721</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>0.010261427851775886</v>
+        <v>0.010259437150473621</v>
       </c>
       <c r="B70">
-        <v>0.0071478866305622266</v>
+        <v>0.0071466054799865656</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>0.0094063088641278946</v>
+        <v>0.00940448405460082</v>
       </c>
       <c r="B71">
-        <v>0.0068013582332202274</v>
+        <v>0.0068001423969278867</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>0.0085511898764799033</v>
+        <v>0.0085495309587280167</v>
       </c>
       <c r="B72">
-        <v>0.0064159446193156854</v>
+        <v>0.0064148012681935684</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>0.0076960708888319128</v>
+        <v>0.0076945778628552154</v>
       </c>
       <c r="B73">
-        <v>0.005989261793410007</v>
+        <v>0.0059881984867384414</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>0.0068409519011839231</v>
+        <v>0.0068396247669824141</v>
       </c>
       <c r="B74">
-        <v>0.0055185347488315491</v>
+        <v>0.0055175594861905167</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>0.0059858329135359326</v>
+        <v>0.0059846716711096119</v>
       </c>
       <c r="B75">
-        <v>0.0050005628801857221</v>
+        <v>0.0049996841518122354</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>0.005130713925887943</v>
+        <v>0.0051297185752368106</v>
       </c>
       <c r="B76">
-        <v>0.004431716547073525</v>
+        <v>0.0044309433737734043</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>0.0042755949382399516</v>
+        <v>0.0042747654793640084</v>
       </c>
       <c r="B77">
-        <v>0.0038079952183393659</v>
+        <v>0.0038073371653604016</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>0.0034204759505919616</v>
+        <v>0.003419812383491207</v>
       </c>
       <c r="B78">
-        <v>0.0031177063741721668</v>
+        <v>0.003117174748966499</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>0.0025653569629439715</v>
+        <v>0.0025648592876184053</v>
       </c>
       <c r="B79">
-        <v>0.0023547662531457026</v>
+        <v>0.0023543729337058869</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>0.0017102379752959808</v>
+        <v>0.0017099061917456035</v>
       </c>
       <c r="B80">
-        <v>0.0015079706392867721</v>
+        <v>0.0015077283380253458</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>0.00085511898764799039</v>
+        <v>0.00085495309587280176</v>
       </c>
       <c r="B81">
-        <v>0.00058282542065090292</v>
+        <v>0.00058274345425747293</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-9.4937278888095369E-19</v>
+        <v>9.4918861201254331E-19</v>
       </c>
     </row>
   </sheetData>
@@ -1681,647 +1681,647 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-1.74479323361905E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.00078578501567653158</v>
+        <v>0.00078563257458581749</v>
       </c>
       <c r="B2">
-        <v>0.0020682123229978466</v>
+        <v>0.002069604429622117</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.0015715700313530632</v>
+        <v>0.001571265149171635</v>
       </c>
       <c r="B3">
-        <v>0.0034408723146141084</v>
+        <v>0.0034431655766743183</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>0.0023573550470295948</v>
+        <v>0.0023568977237574526</v>
       </c>
       <c r="B4">
-        <v>0.0045782908274619675</v>
+        <v>0.0045811987401758979</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>0.0031431400627061263</v>
+        <v>0.00314253029834327</v>
       </c>
       <c r="B5">
-        <v>0.0055470773145441668</v>
+        <v>0.0055504222241397764</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>0.0039289250783826578</v>
+        <v>0.0039281628729290873</v>
       </c>
       <c r="B6">
-        <v>0.0063886405582224354</v>
+        <v>0.006392311612739305</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>0.00471471009405919</v>
+        <v>0.0047137954475149051</v>
       </c>
       <c r="B7">
-        <v>0.0071209550121441563</v>
+        <v>0.0071248728995877029</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>0.0055004951097357216</v>
+        <v>0.0054994280221007229</v>
       </c>
       <c r="B8">
-        <v>0.0077669136156043239</v>
+        <v>0.0077710262443595052</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>0.0062862801254122526</v>
+        <v>0.00628506059668654</v>
       </c>
       <c r="B9">
-        <v>0.0083350423020947754</v>
+        <v>0.0083393099524333072</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>0.0070720651410887845</v>
+        <v>0.0070706931712723577</v>
       </c>
       <c r="B10">
-        <v>0.0088326262428933891</v>
+        <v>0.008837018485352335</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>0.0078578501567653156</v>
+        <v>0.0078563257458581746</v>
       </c>
       <c r="B11">
-        <v>0.0092659006394919755</v>
+        <v>0.0092703939923117033</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>0.0086436351724418475</v>
+        <v>0.0086419583204439925</v>
       </c>
       <c r="B12">
-        <v>0.0096402113003587926</v>
+        <v>0.00964478746548419</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>0.00942942018811838</v>
+        <v>0.00942759089502981</v>
       </c>
       <c r="B13">
-        <v>0.0099601500684226539</v>
+        <v>0.0099647946100876374</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>0.010215205203794911</v>
+        <v>0.010213223469615628</v>
       </c>
       <c r="B14">
-        <v>0.010229669608667386</v>
+        <v>0.0102343709660648</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>0.011000990219471443</v>
+        <v>0.010998856044201446</v>
       </c>
       <c r="B15">
-        <v>0.010452181778064642</v>
+        <v>0.010456930528687724</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>0.011786775235147973</v>
+        <v>0.011784488618787262</v>
       </c>
       <c r="B16">
-        <v>0.010630643586262312</v>
+        <v>0.010635431897551157</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>0.012572560250824505</v>
+        <v>0.01257012119337308</v>
       </c>
       <c r="B17">
-        <v>0.010767634620478665</v>
+        <v>0.010772455844502097</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>0.013358345266501037</v>
+        <v>0.013355753767958898</v>
       </c>
       <c r="B18">
-        <v>0.010865429834233388</v>
+        <v>0.010870278214124307</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>0.014144130282177569</v>
+        <v>0.014141386342544715</v>
       </c>
       <c r="B19">
-        <v>0.010913020826921065</v>
+        <v>0.010917889652379643</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>0.014929915297854101</v>
+        <v>0.014927018917130533</v>
       </c>
       <c r="B20">
-        <v>0.010922939272517841</v>
+        <v>0.010927823799550793</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>0.015715700313530631</v>
+        <v>0.015712651491716349</v>
       </c>
       <c r="B21">
-        <v>0.010897338682494527</v>
+        <v>0.010902234479118757</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>0.016501485329207165</v>
+        <v>0.016498284066302167</v>
       </c>
       <c r="B22">
-        <v>0.010837608760205078</v>
+        <v>0.010842511565312374</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>0.017287270344883695</v>
+        <v>0.017283916640887985</v>
       </c>
       <c r="B23">
-        <v>0.010731838265302836</v>
+        <v>0.010736742157417368</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>0.018073055360560229</v>
+        <v>0.018069549215473803</v>
       </c>
       <c r="B24">
-        <v>0.010586498635184013</v>
+        <v>0.010591398071318686</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>0.018858840376236759</v>
+        <v>0.018855181790059621</v>
       </c>
       <c r="B25">
-        <v>0.010408070563665771</v>
+        <v>0.010412960524518355</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>0.019644625391913289</v>
+        <v>0.019640814364645438</v>
       </c>
       <c r="B26">
-        <v>0.010194834659731488</v>
+        <v>0.010199709594431216</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>0.020430410407589823</v>
+        <v>0.020426446939231256</v>
       </c>
       <c r="B27">
-        <v>0.0099271726490318454</v>
+        <v>0.0099320223169003258</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>0.021216195423266353</v>
+        <v>0.021212079513817074</v>
       </c>
       <c r="B28">
-        <v>0.0096252744801377053</v>
+        <v>0.009630091178984829</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>0.022001980438942886</v>
+        <v>0.021997712088402892</v>
       </c>
       <c r="B29">
-        <v>0.0092898598554299119</v>
+        <v>0.009294635696134923</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>0.022787765454619417</v>
+        <v>0.02278334466298871</v>
       </c>
       <c r="B30">
-        <v>0.0088937269633443932</v>
+        <v>0.0088984448057059552</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>0.023573550470295947</v>
+        <v>0.023568977237574524</v>
       </c>
       <c r="B31">
-        <v>0.0084547462003266086</v>
+        <v>0.00845939083335702</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>0.02435933548597248</v>
+        <v>0.024354609812160342</v>
       </c>
       <c r="B32">
-        <v>0.0079779638120526034</v>
+        <v>0.0079825209194575551</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>0.02514512050164901</v>
+        <v>0.02514024238674616</v>
       </c>
       <c r="B33">
-        <v>0.0074301809066981677</v>
+        <v>0.0074346183237088267</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>0.025930905517325544</v>
+        <v>0.025925874961331977</v>
       </c>
       <c r="B34">
-        <v>0.0068255538531164246</v>
+        <v>0.0068298381903602375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>0.026716690533002074</v>
+        <v>0.026711507535917795</v>
       </c>
       <c r="B35">
-        <v>0.0061737595007625174</v>
+        <v>0.0061778608352857688</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>0.027502475548678604</v>
+        <v>0.02749714011050361</v>
       </c>
       <c r="B36">
-        <v>0.0054234378397915251</v>
+        <v>0.0054272795892643944</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>0.028288260564355138</v>
+        <v>0.028282772685089431</v>
       </c>
       <c r="B37">
-        <v>0.0045920138176198952</v>
+        <v>0.0045955100788749</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>0.029074045580031668</v>
+        <v>0.029068405259675249</v>
       </c>
       <c r="B38">
-        <v>0.0036920849916555706</v>
+        <v>0.0036951579798751612</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>0.029859830595708202</v>
+        <v>0.029854037834261066</v>
       </c>
       <c r="B39">
-        <v>0.0026177455128106797</v>
+        <v>0.0026201314046953006</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>0.030645615611384732</v>
+        <v>0.030639670408846884</v>
       </c>
       <c r="B40">
-        <v>0.0015434060339657894</v>
+        <v>0.0015451048295154408</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>0.031431400627061262</v>
+        <v>0.0314253029834327</v>
       </c>
       <c r="B41">
-        <v>0.00046906655512090321</v>
+        <v>0.00047007825433558517</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>0.031431400627061262</v>
+        <v>0.0314253029834327</v>
       </c>
       <c r="B42">
-        <v>0.00038286232623759828</v>
+        <v>0.00038389074894078321</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>0.030645615611384732</v>
+        <v>0.030639670408846884</v>
       </c>
       <c r="B43">
-        <v>0.0012686146314645702</v>
+        <v>0.00127036673612585</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>0.029859830595708202</v>
+        <v>0.029854037834261066</v>
       </c>
       <c r="B44">
-        <v>0.0021543669366915459</v>
+        <v>0.0021568427233109207</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>0.029074045580031668</v>
+        <v>0.029068405259675249</v>
       </c>
       <c r="B45">
-        <v>0.0030401192419185221</v>
+        <v>0.0030433187104959912</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>0.028288260564355138</v>
+        <v>0.028282772685089431</v>
       </c>
       <c r="B46">
-        <v>0.0037592218848967736</v>
+        <v>0.0037628797065124746</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>0.027502475548678604</v>
+        <v>0.02749714011050361</v>
       </c>
       <c r="B47">
-        <v>0.0044135509994078148</v>
+        <v>0.0044175886653824931</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>0.026716690533002074</v>
+        <v>0.026711507535917795</v>
       </c>
       <c r="B48">
-        <v>0.0049913586698556974</v>
+        <v>0.0049956893883309579</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>0.025930905517325544</v>
+        <v>0.025925874961331977</v>
       </c>
       <c r="B49">
-        <v>0.0054773038934884935</v>
+        <v>0.0054818497891615196</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>0.02514512050164901</v>
+        <v>0.02514024238674616</v>
       </c>
       <c r="B50">
-        <v>0.0059196548740462788</v>
+        <v>0.0059243853307960215</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>0.02435933548597248</v>
+        <v>0.024354609812160342</v>
       </c>
       <c r="B51">
-        <v>0.0063096194821924472</v>
+        <v>0.0063145002458446639</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>0.023573550470295947</v>
+        <v>0.023568977237574524</v>
       </c>
       <c r="B52">
-        <v>0.0066349235475298444</v>
+        <v>0.0066399212233703925</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>0.022787765454619417</v>
+        <v>0.02278334466298871</v>
       </c>
       <c r="B53">
-        <v>0.00692612865272923</v>
+        <v>0.0069312282061524356</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>0.022001980438942886</v>
+        <v>0.021997712088402892</v>
       </c>
       <c r="B54">
-        <v>0.0071788012341906923</v>
+        <v>0.0071839866170381</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>0.021216195423266353</v>
+        <v>0.021212079513817074</v>
       </c>
       <c r="B55">
-        <v>0.0073776188752303984</v>
+        <v>0.0073828716158257438</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>0.020430410407589823</v>
+        <v>0.020426446939231256</v>
       </c>
       <c r="B56">
-        <v>0.0075470995577661759</v>
+        <v>0.007552410956172621</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>0.019644625391913289</v>
+        <v>0.019640814364645438</v>
       </c>
       <c r="B57">
-        <v>0.0076867148630891729</v>
+        <v>0.0076920763691917839</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>0.018858840376236759</v>
+        <v>0.018855181790059621</v>
       </c>
       <c r="B58">
-        <v>0.0077795904779695123</v>
+        <v>0.0077849903599368931</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>0.018073055360560229</v>
+        <v>0.018069549215473803</v>
       </c>
       <c r="B59">
-        <v>0.0078431296986770319</v>
+        <v>0.0078485613441877655</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>0.017287270344883695</v>
+        <v>0.017283916640887985</v>
       </c>
       <c r="B60">
-        <v>0.0078790082998237577</v>
+        <v>0.00788446563658649</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>0.016501485329207165</v>
+        <v>0.016498284066302167</v>
       </c>
       <c r="B61">
-        <v>0.0078822132415157838</v>
+        <v>0.0078876893888316646</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>0.015715700313530631</v>
+        <v>0.015712651491716349</v>
       </c>
       <c r="B62">
-        <v>0.0078482280616671129</v>
+        <v>0.0078537153810863489</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>0.014929915297854101</v>
+        <v>0.014927018917130533</v>
       </c>
       <c r="B63">
-        <v>0.0077872040818799107</v>
+        <v>0.0077926969367418672</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>0.014144130282177569</v>
+        <v>0.014141386342544715</v>
       </c>
       <c r="B64">
-        <v>0.0076983955844467308</v>
+        <v>0.0077038880422836608</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>0.013358345266501037</v>
+        <v>0.013355753767958898</v>
       </c>
       <c r="B65">
-        <v>0.0075805682151591954</v>
+        <v>0.0075860538531780592</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>0.012572560250824505</v>
+        <v>0.01257012119337308</v>
       </c>
       <c r="B66">
-        <v>0.0074250175385348607</v>
+        <v>0.0074304872251576611</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>0.011786775235147973</v>
+        <v>0.011784488618787262</v>
       </c>
       <c r="B67">
-        <v>0.0072407329063276559</v>
+        <v>0.0072461788551015163</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>0.011000990219471443</v>
+        <v>0.010998856044201446</v>
       </c>
       <c r="B68">
-        <v>0.0070265788992141323</v>
+        <v>0.0070319922115542081</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>0.010215205203794911</v>
+        <v>0.010213223469615628</v>
       </c>
       <c r="B69">
-        <v>0.0067813028008427969</v>
+        <v>0.0067866731361245934</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>0.00942942018811838</v>
+        <v>0.00942759089502981</v>
       </c>
       <c r="B70">
-        <v>0.0065034914454347118</v>
+        <v>0.006508806573583532</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>0.0086436351724418475</v>
+        <v>0.0086419583204439925</v>
       </c>
       <c r="B71">
-        <v>0.0061915289139931277</v>
+        <v>0.00619677411822466</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>0.0078578501567653156</v>
+        <v>0.0078563257458581746</v>
       </c>
       <c r="B72">
-        <v>0.0058435550744378381</v>
+        <v>0.0058487123570606665</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>0.0070720651410887845</v>
+        <v>0.0070706931712723577</v>
       </c>
       <c r="B73">
-        <v>0.0054574269463938813</v>
+        <v>0.0054624739723519661</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>0.0062862801254122526</v>
+        <v>0.00628506059668654</v>
       </c>
       <c r="B74">
-        <v>0.0050306876561280415</v>
+        <v>0.0050355963462119088</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>0.0055004951097357216</v>
+        <v>0.0054994280221007229</v>
       </c>
       <c r="B75">
-        <v>0.0045605520295887852</v>
+        <v>0.00456528668758561</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>0.00471471009405919</v>
+        <v>0.0047137954475149051</v>
       </c>
       <c r="B76">
-        <v>0.0040439247453141255</v>
+        <v>0.0040484395719212829</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>0.0039289250783826578</v>
+        <v>0.0039281628729290873</v>
       </c>
       <c r="B77">
-        <v>0.0034774782175359</v>
+        <v>0.003481714033092503</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>0.0031431400627061263</v>
+        <v>0.00314253029834327</v>
       </c>
       <c r="B78">
-        <v>0.0028511597060955933</v>
+        <v>0.002855027619582228</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>0.0023573550470295948</v>
+        <v>0.0023568977237574526</v>
       </c>
       <c r="B79">
-        <v>0.0021602767733415805</v>
+        <v>0.0021636537770822147</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>0.0015715700313530632</v>
+        <v>0.001571265149171635</v>
       </c>
       <c r="B80">
-        <v>0.0013961215956252049</v>
+        <v>0.0013988115361962324</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>0.00078578501567653158</v>
+        <v>0.00078563257458581749</v>
       </c>
       <c r="B81">
-        <v>0.00056481491805431764</v>
+        <v>0.000566498681474803</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-1.74479323361905E-18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
